--- a/Employee_Reports_wi52/Catalino Mendoza Rojas Q0562.xlsx
+++ b/Employee_Reports_wi52/Catalino Mendoza Rojas Q0562.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-173</v>
+        <v>-181</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="5" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>-55</v>
+        <v>-63</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="5" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="5" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
@@ -1166,11 +1166,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1215,11 +1215,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1264,11 +1264,11 @@
         </is>
       </c>
       <c r="H17" s="5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
@@ -1313,11 +1313,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1362,11 +1362,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1460,11 +1460,11 @@
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
@@ -1510,11 +1510,11 @@
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>-311</v>
+        <v>-319</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1559,11 +1559,11 @@
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-69</v>
+        <v>-77</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1608,11 +1608,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
@@ -1645,11 +1645,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>-373</v>
+        <v>-381</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1682,11 +1682,11 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-157</v>
+        <v>-165</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1731,11 +1731,11 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-157</v>
+        <v>-165</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -1780,11 +1780,11 @@
         </is>
       </c>
       <c r="H28" s="3" t="n">
-        <v>-182</v>
+        <v>-190</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -1829,11 +1829,11 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-69</v>
+        <v>-77</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -1878,11 +1878,11 @@
         </is>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-21</v>
+        <v>-29</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -1927,11 +1927,11 @@
         </is>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-19</v>
+        <v>-27</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -1964,11 +1964,11 @@
         </is>
       </c>
       <c r="H32" s="3" t="n">
-        <v>-23</v>
+        <v>-31</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -1979,78 +1979,78 @@
       <c r="K32" s="3" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n">
+      <c r="A33" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr"/>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G33" s="4" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H33" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I33" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K33" s="4" t="inlineStr"/>
+      <c r="H33" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n">
+      <c r="A34" s="5" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr"/>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2025</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="G34" s="5" t="inlineStr">
         <is>
           <t>01-Oct-2026</t>
         </is>
       </c>
-      <c r="H34" s="4" t="n">
-        <v>42</v>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr"/>
+      <c r="H34" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>EXPIRING SOON</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
@@ -2087,11 +2087,11 @@
         </is>
       </c>
       <c r="H35" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
@@ -2136,11 +2136,11 @@
         </is>
       </c>
       <c r="H36" s="5" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
@@ -2173,11 +2173,11 @@
         </is>
       </c>
       <c r="H37" s="5" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
@@ -2222,11 +2222,11 @@
         </is>
       </c>
       <c r="H38" s="4" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
@@ -2237,41 +2237,41 @@
       <c r="K38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr"/>
-      <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr"/>
+      <c r="E39" s="3" t="inlineStr"/>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>25-Aug-2024</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>25-Aug-2026</t>
         </is>
       </c>
-      <c r="H39" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K39" s="5" t="inlineStr"/>
+      <c r="H39" s="3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
